--- a/Design/Configs/MapId.xlsx
+++ b/Design/Configs/MapId.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F65AD90-1DD5-4950-A1AB-C6F5B3FCAE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-28800" yWindow="-30" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,13 +54,17 @@
   </si>
   <si>
     <t>BigSuperSolarSystem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -377,8 +382,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.25" customWidth="1"/>
@@ -499,83 +504,15 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11">
         <v>4</v>
       </c>
     </row>

--- a/Design/Configs/MapId.xlsx
+++ b/Design/Configs/MapId.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F65AD90-1DD5-4950-A1AB-C6F5B3FCAE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68845A60-9857-4ADD-AE69-AAF8B9B4080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="-30" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="-90" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,6 +58,10 @@
   </si>
   <si>
     <t>Map_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_TreasureTest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -383,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.25" customWidth="1"/>
@@ -506,13 +510,24 @@
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
     </row>

--- a/Design/Configs/MapId.xlsx
+++ b/Design/Configs/MapId.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68845A60-9857-4ADD-AE69-AAF8B9B4080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16509ECE-C336-4E91-8410-B383EC5C2671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="-90" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,30 +38,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>PlayerCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperSolarSystem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_TreasureTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>SolarSystem</t>
-  </si>
-  <si>
-    <t>ThreeBodySystem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperSolarSystem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BigSuperSolarSystem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_TreasureTest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -387,21 +380,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="20.25" customWidth="1"/>
-    <col min="4" max="4" width="25.25" customWidth="1"/>
-    <col min="5" max="5" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="25.21875" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" customWidth="1"/>
+    <col min="4" max="4" width="25.21875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,119 +408,51 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8">
         <v>4</v>
       </c>
     </row>
